--- a/04 - Vencimientos de personal y vehículos.xlsx
+++ b/04 - Vencimientos de personal y vehículos.xlsx
@@ -664,7 +664,7 @@
     <row r="13" ht="30" customHeight="1" s="19">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Si te sirvió y querés colaborar, mi alias de Mercado Pago es igna.pelliza. Gracias.</t>
+          <t>¡Gracias! Si te sirvió y querés colaborar, mi alias de Mercado Pago es:  igna.pelliza</t>
         </is>
       </c>
     </row>
